--- a/research-register/Search_Demand_Analysis_Class_Work_2.xlsx
+++ b/research-register/Search_Demand_Analysis_Class_Work_2.xlsx
@@ -34,26 +34,26 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="001A56DB"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
     </font>
     <font>
-      <name val="Courier New"/>
-      <color rgb="00404040"/>
+      <b val="1"/>
+      <color rgb="001A56DB"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
+      <name val="Courier New"/>
+      <color rgb="00000000"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00404040"/>
+      <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,18 +61,11 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
+      <patternFill patternType="solid"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
+        <fgColor rgb="00EEF4FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,16 +79,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
@@ -132,13 +125,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,11 +246,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="10A37F"/>
+              <a:srgbClr val="1A56DB"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="10A37F"/>
+                <a:srgbClr val="1A56DB"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
